--- a/InfoTabloServer/bin/Debug/net6.0/Raspisanie/_19_24_dec.xlsx
+++ b/InfoTabloServer/bin/Debug/net6.0/Raspisanie/_19_24_dec.xlsx
@@ -2591,7 +2591,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{3fb5adea-d6b8-4e0a-8cbb-d57ed3be70d1}" mc:Ignorable="x14ac xr xr2 xr3">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{7328ed65-d3a1-4ee6-90aa-d9c70f5e9da4}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr codeName="Лист1">
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -6712,7 +6712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{e00962f3-b609-4417-8c89-aad44aff3bd5}" mc:Ignorable="x14ac xr xr2 xr3">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{a6ff9fda-53a4-4e37-a7c6-8cde10bb8029}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
